--- a/data/UNSD.xlsx
+++ b/data/UNSD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaisdiaz/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370E9C93-6676-6C45-90C5-5E8D854A44A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C59C23-4387-E64C-833D-38D09795A279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2474,12 +2474,6 @@
     <t>M49 Region</t>
   </si>
   <si>
-    <t>Country/Area</t>
-  </si>
-  <si>
-    <t>M49 Country/Area Code</t>
-  </si>
-  <si>
     <t>XKX</t>
   </si>
   <si>
@@ -2576,7 +2570,13 @@
     <t>Czechoslovakia (historic)</t>
   </si>
   <si>
-    <t>M49 Country/Area</t>
+    <t>M49 Area Code</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>M49 Area</t>
   </si>
 </sst>
 </file>
@@ -2726,8 +2726,8 @@
     <tableColumn id="7" xr3:uid="{D9C63778-5713-4439-BC7C-BE648FBE9FBB}" name="M49 Intermediate Region"/>
     <tableColumn id="8" xr3:uid="{72755315-FA98-474A-A36F-611FA893A4F8}" name="Geographic Subregion" dataDxfId="7"/>
     <tableColumn id="12" xr3:uid="{F4D6B531-89E7-4638-9C63-4263AB3084AF}" name="ISO-alpha3 Code" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{0E6BCC5D-0A0A-40BC-89CD-EB10EF634F3D}" name="Country/Area"/>
-    <tableColumn id="10" xr3:uid="{06A9D368-6678-48B0-9E4C-7F7BB9F7AB1E}" name="M49 Country/Area Code" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{0E6BCC5D-0A0A-40BC-89CD-EB10EF634F3D}" name="Area"/>
+    <tableColumn id="10" xr3:uid="{06A9D368-6678-48B0-9E4C-7F7BB9F7AB1E}" name="M49 Area Code" dataDxfId="5"/>
     <tableColumn id="11" xr3:uid="{821252A1-E0D0-4EBA-AE1F-DF56D5DDD6C5}" name="ISO-alpha2 Code"/>
     <tableColumn id="13" xr3:uid="{BAF06E67-24B2-496C-9648-7FB315749EF7}" name="M49"/>
     <tableColumn id="16" xr3:uid="{33408CEA-99C9-48FC-8725-6F4FACED50D5}" name="UN Sovereign States (bool)" dataDxfId="4"/>
@@ -2736,13 +2736,13 @@
       <calculatedColumnFormula>IF(Tabelle1[[#This Row],[UN Sovereign States (bool)]]="x", Tabelle1[[#This Row],[ISO-alpha3 Code]], Tabelle1[[#This Row],[Occupier]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{F9424B07-78F3-4C44-9B51-D11C09BC0F7F}" name="UN Sovereign State" dataDxfId="2">
-      <calculatedColumnFormula>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{E71717EC-1BAD-844F-8A5C-2D2635030C6C}" name="M49 Country/Area" dataDxfId="0">
-      <calculatedColumnFormula>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</calculatedColumnFormula>
+    <tableColumn id="19" xr3:uid="{E71717EC-1BAD-844F-8A5C-2D2635030C6C}" name="M49 Area" dataDxfId="1">
+      <calculatedColumnFormula>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{DFFCB14A-BB9A-4F38-A973-FF75EE5973FA}" name="Pop Data" dataDxfId="1">
-      <calculatedColumnFormula>Tabelle1[[#This Row],[Country/Area]]</calculatedColumnFormula>
+    <tableColumn id="18" xr3:uid="{DFFCB14A-BB9A-4F38-A973-FF75EE5973FA}" name="Pop Data" dataDxfId="0">
+      <calculatedColumnFormula>Tabelle1[[#This Row],[Area]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3118,34 +3118,34 @@
         <v>1</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>812</v>
+        <v>845</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>813</v>
+        <v>844</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>803</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>846</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
@@ -3196,15 +3196,15 @@
         <v>AFG</v>
       </c>
       <c r="Q2" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Afghanistan</v>
       </c>
       <c r="R2" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Afghanistan</v>
       </c>
       <c r="S2" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Afghanistan</v>
       </c>
     </row>
@@ -3257,15 +3257,15 @@
         <v>DNK</v>
       </c>
       <c r="Q3" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Denmark</v>
       </c>
       <c r="R3" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Åland Islands</v>
       </c>
       <c r="S3" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Åland Islands</v>
       </c>
     </row>
@@ -3317,15 +3317,15 @@
         <v>ALB</v>
       </c>
       <c r="Q4" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Albania</v>
       </c>
       <c r="R4" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Albania</v>
       </c>
       <c r="S4" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Albania</v>
       </c>
     </row>
@@ -3377,15 +3377,15 @@
         <v>DZA</v>
       </c>
       <c r="Q5" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Algeria</v>
       </c>
       <c r="R5" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Algeria</v>
       </c>
       <c r="S5" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Algeria</v>
       </c>
     </row>
@@ -3438,15 +3438,15 @@
         <v>USA</v>
       </c>
       <c r="Q6" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United States of America</v>
       </c>
       <c r="R6" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>American Samoa</v>
       </c>
       <c r="S6" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>American Samoa</v>
       </c>
     </row>
@@ -3498,15 +3498,15 @@
         <v>AND</v>
       </c>
       <c r="Q7" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Andorra</v>
       </c>
       <c r="R7" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Andorra</v>
       </c>
       <c r="S7" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Andorra</v>
       </c>
     </row>
@@ -3558,15 +3558,15 @@
         <v>AGO</v>
       </c>
       <c r="Q8" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Angola</v>
       </c>
       <c r="R8" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Angola</v>
       </c>
       <c r="S8" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Angola</v>
       </c>
     </row>
@@ -3619,15 +3619,15 @@
         <v>GBR</v>
       </c>
       <c r="Q9" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R9" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Anguilla</v>
       </c>
       <c r="S9" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Anguilla</v>
       </c>
     </row>
@@ -3677,15 +3677,15 @@
         <v>0</v>
       </c>
       <c r="Q10" t="e">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="R10" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Antarctica</v>
       </c>
       <c r="S10" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Antarctica</v>
       </c>
     </row>
@@ -3737,15 +3737,15 @@
         <v>ATG</v>
       </c>
       <c r="Q11" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Antigua and Barbuda</v>
       </c>
       <c r="R11" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Antigua and Barbuda</v>
       </c>
       <c r="S11" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Antigua and Barbuda</v>
       </c>
     </row>
@@ -3797,15 +3797,15 @@
         <v>ARG</v>
       </c>
       <c r="Q12" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Argentina</v>
       </c>
       <c r="R12" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Argentina</v>
       </c>
       <c r="S12" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Argentina</v>
       </c>
     </row>
@@ -3857,15 +3857,15 @@
         <v>ARM</v>
       </c>
       <c r="Q13" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Armenia</v>
       </c>
       <c r="R13" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Armenia</v>
       </c>
       <c r="S13" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Armenia</v>
       </c>
     </row>
@@ -3918,15 +3918,15 @@
         <v>NLD</v>
       </c>
       <c r="Q14" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Netherlands (Kingdom of the)</v>
       </c>
       <c r="R14" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Aruba</v>
       </c>
       <c r="S14" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Aruba</v>
       </c>
     </row>
@@ -3978,15 +3978,15 @@
         <v>AUS</v>
       </c>
       <c r="Q15" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Australia</v>
       </c>
       <c r="R15" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Australia</v>
       </c>
       <c r="S15" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Australia</v>
       </c>
     </row>
@@ -4038,15 +4038,15 @@
         <v>AUT</v>
       </c>
       <c r="Q16" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Austria</v>
       </c>
       <c r="R16" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Austria</v>
       </c>
       <c r="S16" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Austria</v>
       </c>
     </row>
@@ -4098,15 +4098,15 @@
         <v>AZE</v>
       </c>
       <c r="Q17" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Azerbaijan</v>
       </c>
       <c r="R17" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Azerbaijan</v>
       </c>
       <c r="S17" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Azerbaijan</v>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
         <v>810</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>804</v>
@@ -4153,15 +4153,15 @@
         <v>PRT</v>
       </c>
       <c r="Q18" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Portugal</v>
       </c>
       <c r="R18" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>not in M49 standard (2025)</v>
       </c>
       <c r="S18" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Azores Islands</v>
       </c>
     </row>
@@ -4213,15 +4213,15 @@
         <v>BHS</v>
       </c>
       <c r="Q19" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Bahamas</v>
       </c>
       <c r="R19" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bahamas</v>
       </c>
       <c r="S19" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bahamas</v>
       </c>
     </row>
@@ -4273,15 +4273,15 @@
         <v>BHR</v>
       </c>
       <c r="Q20" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Bahrain</v>
       </c>
       <c r="R20" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bahrain</v>
       </c>
       <c r="S20" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bahrain</v>
       </c>
     </row>
@@ -4333,15 +4333,15 @@
         <v>BGD</v>
       </c>
       <c r="Q21" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Bangladesh</v>
       </c>
       <c r="R21" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bangladesh</v>
       </c>
       <c r="S21" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bangladesh</v>
       </c>
     </row>
@@ -4393,15 +4393,15 @@
         <v>BRB</v>
       </c>
       <c r="Q22" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Barbados</v>
       </c>
       <c r="R22" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Barbados</v>
       </c>
       <c r="S22" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Barbados</v>
       </c>
     </row>
@@ -4453,15 +4453,15 @@
         <v>BLR</v>
       </c>
       <c r="Q23" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Belarus</v>
       </c>
       <c r="R23" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Belarus</v>
       </c>
       <c r="S23" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Belarus</v>
       </c>
     </row>
@@ -4513,15 +4513,15 @@
         <v>BEL</v>
       </c>
       <c r="Q24" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Belgium</v>
       </c>
       <c r="R24" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Belgium</v>
       </c>
       <c r="S24" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Belgium</v>
       </c>
     </row>
@@ -4573,15 +4573,15 @@
         <v>BLZ</v>
       </c>
       <c r="Q25" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Belize</v>
       </c>
       <c r="R25" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Belize</v>
       </c>
       <c r="S25" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Belize</v>
       </c>
     </row>
@@ -4633,15 +4633,15 @@
         <v>BEN</v>
       </c>
       <c r="Q26" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Benin</v>
       </c>
       <c r="R26" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Benin</v>
       </c>
       <c r="S26" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Benin</v>
       </c>
     </row>
@@ -4694,15 +4694,15 @@
         <v>GBR</v>
       </c>
       <c r="Q27" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R27" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bermuda</v>
       </c>
       <c r="S27" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bermuda</v>
       </c>
     </row>
@@ -4754,15 +4754,15 @@
         <v>BTN</v>
       </c>
       <c r="Q28" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Bhutan</v>
       </c>
       <c r="R28" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bhutan</v>
       </c>
       <c r="S28" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bhutan</v>
       </c>
     </row>
@@ -4814,15 +4814,15 @@
         <v>BOL</v>
       </c>
       <c r="Q29" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Bolivia (Plurinational State of)</v>
       </c>
       <c r="R29" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bolivia (Plurinational State of)</v>
       </c>
       <c r="S29" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bolivia (Plurinational State of)</v>
       </c>
     </row>
@@ -4875,15 +4875,15 @@
         <v>NLD</v>
       </c>
       <c r="Q30" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Netherlands (Kingdom of the)</v>
       </c>
       <c r="R30" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bonaire, Sint Eustatius and Saba</v>
       </c>
       <c r="S30" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bonaire, Sint Eustatius and Saba</v>
       </c>
     </row>
@@ -4935,15 +4935,15 @@
         <v>BIH</v>
       </c>
       <c r="Q31" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Bosnia and Herzegovina</v>
       </c>
       <c r="R31" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bosnia and Herzegovina</v>
       </c>
       <c r="S31" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bosnia and Herzegovina</v>
       </c>
     </row>
@@ -4995,15 +4995,15 @@
         <v>BWA</v>
       </c>
       <c r="Q32" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Botswana</v>
       </c>
       <c r="R32" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Botswana</v>
       </c>
       <c r="S32" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Botswana</v>
       </c>
     </row>
@@ -5056,15 +5056,15 @@
         <v>NOR</v>
       </c>
       <c r="Q33" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Norway</v>
       </c>
       <c r="R33" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bouvet Island</v>
       </c>
       <c r="S33" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bouvet Island</v>
       </c>
     </row>
@@ -5116,15 +5116,15 @@
         <v>BRA</v>
       </c>
       <c r="Q34" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Brazil</v>
       </c>
       <c r="R34" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Brazil</v>
       </c>
       <c r="S34" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Brazil</v>
       </c>
     </row>
@@ -5177,15 +5177,15 @@
         <v>GBR</v>
       </c>
       <c r="Q35" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R35" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>British Indian Ocean Territory</v>
       </c>
       <c r="S35" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>British Indian Ocean Territory</v>
       </c>
     </row>
@@ -5238,15 +5238,15 @@
         <v>GBR</v>
       </c>
       <c r="Q36" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R36" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>British Virgin Islands</v>
       </c>
       <c r="S36" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>British Virgin Islands</v>
       </c>
     </row>
@@ -5298,15 +5298,15 @@
         <v>BRN</v>
       </c>
       <c r="Q37" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Brunei Darussalam</v>
       </c>
       <c r="R37" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Brunei Darussalam</v>
       </c>
       <c r="S37" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Brunei Darussalam</v>
       </c>
     </row>
@@ -5358,15 +5358,15 @@
         <v>BGR</v>
       </c>
       <c r="Q38" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Bulgaria</v>
       </c>
       <c r="R38" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Bulgaria</v>
       </c>
       <c r="S38" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Bulgaria</v>
       </c>
     </row>
@@ -5418,15 +5418,15 @@
         <v>BFA</v>
       </c>
       <c r="Q39" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Burkina Faso</v>
       </c>
       <c r="R39" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Burkina Faso</v>
       </c>
       <c r="S39" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Burkina Faso</v>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
         <v>BDI</v>
       </c>
       <c r="Q40" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Burundi</v>
       </c>
       <c r="R40" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Burundi</v>
       </c>
       <c r="S40" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Burundi</v>
       </c>
     </row>
@@ -5538,15 +5538,15 @@
         <v>CPV</v>
       </c>
       <c r="Q41" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Cabo Verde</v>
       </c>
       <c r="R41" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Cabo Verde</v>
       </c>
       <c r="S41" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Cabo Verde</v>
       </c>
     </row>
@@ -5598,15 +5598,15 @@
         <v>KHM</v>
       </c>
       <c r="Q42" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Cambodia</v>
       </c>
       <c r="R42" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Cambodia</v>
       </c>
       <c r="S42" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Cambodia</v>
       </c>
     </row>
@@ -5658,15 +5658,15 @@
         <v>CMR</v>
       </c>
       <c r="Q43" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Cameroon</v>
       </c>
       <c r="R43" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Cameroon</v>
       </c>
       <c r="S43" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Cameroon</v>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
         <v>CAN</v>
       </c>
       <c r="Q44" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Canada</v>
       </c>
       <c r="R44" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Canada</v>
       </c>
       <c r="S44" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Canada</v>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
         <v>791</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>805</v>
@@ -5772,15 +5772,15 @@
         <v>ESP</v>
       </c>
       <c r="Q45" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Spain</v>
       </c>
       <c r="R45" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>not in M49 standard (2025)</v>
       </c>
       <c r="S45" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Canary Islands</v>
       </c>
     </row>
@@ -5833,15 +5833,15 @@
         <v>GBR</v>
       </c>
       <c r="Q46" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R46" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Cayman Islands</v>
       </c>
       <c r="S46" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Cayman Islands</v>
       </c>
     </row>
@@ -5893,15 +5893,15 @@
         <v>CAF</v>
       </c>
       <c r="Q47" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Central African Republic</v>
       </c>
       <c r="R47" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Central African Republic</v>
       </c>
       <c r="S47" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Central African Republic</v>
       </c>
     </row>
@@ -5953,15 +5953,15 @@
         <v>TCD</v>
       </c>
       <c r="Q48" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Chad</v>
       </c>
       <c r="R48" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Chad</v>
       </c>
       <c r="S48" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Chad</v>
       </c>
     </row>
@@ -6013,15 +6013,15 @@
         <v>CHL</v>
       </c>
       <c r="Q49" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Chile</v>
       </c>
       <c r="R49" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Chile</v>
       </c>
       <c r="S49" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Chile</v>
       </c>
     </row>
@@ -6073,15 +6073,15 @@
         <v>CHN</v>
       </c>
       <c r="Q50" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>China</v>
       </c>
       <c r="R50" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>China</v>
       </c>
       <c r="S50" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>China</v>
       </c>
     </row>
@@ -6134,15 +6134,15 @@
         <v>CHN</v>
       </c>
       <c r="Q51" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>China</v>
       </c>
       <c r="R51" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>China, Hong Kong Special Administrative Region</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
@@ -6194,15 +6194,15 @@
         <v>CHN</v>
       </c>
       <c r="Q52" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>China</v>
       </c>
       <c r="R52" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>China, Macao Special Administrative Region</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
@@ -6254,15 +6254,15 @@
         <v>AUS</v>
       </c>
       <c r="Q53" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Australia</v>
       </c>
       <c r="R53" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Christmas Island</v>
       </c>
       <c r="S53" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Christmas Island</v>
       </c>
     </row>
@@ -6315,15 +6315,15 @@
         <v>AUS</v>
       </c>
       <c r="Q54" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Australia</v>
       </c>
       <c r="R54" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Cocos (Keeling) Islands</v>
       </c>
       <c r="S54" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Cocos (Keeling) Islands</v>
       </c>
     </row>
@@ -6375,15 +6375,15 @@
         <v>COL</v>
       </c>
       <c r="Q55" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Colombia</v>
       </c>
       <c r="R55" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Colombia</v>
       </c>
       <c r="S55" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Colombia</v>
       </c>
     </row>
@@ -6435,15 +6435,15 @@
         <v>COM</v>
       </c>
       <c r="Q56" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Comoros</v>
       </c>
       <c r="R56" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Comoros</v>
       </c>
       <c r="S56" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Comoros</v>
       </c>
     </row>
@@ -6495,15 +6495,15 @@
         <v>COG</v>
       </c>
       <c r="Q57" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Congo</v>
       </c>
       <c r="R57" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Congo</v>
       </c>
       <c r="S57" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Congo</v>
       </c>
     </row>
@@ -6556,15 +6556,15 @@
         <v>NZL</v>
       </c>
       <c r="Q58" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>New Zealand</v>
       </c>
       <c r="R58" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Cook Islands</v>
       </c>
       <c r="S58" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Cook Islands</v>
       </c>
     </row>
@@ -6616,15 +6616,15 @@
         <v>CRI</v>
       </c>
       <c r="Q59" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Costa Rica</v>
       </c>
       <c r="R59" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Costa Rica</v>
       </c>
       <c r="S59" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Costa Rica</v>
       </c>
     </row>
@@ -6676,15 +6676,15 @@
         <v>CIV</v>
       </c>
       <c r="Q60" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Côte d’Ivoire</v>
       </c>
       <c r="R60" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Côte d’Ivoire</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.2">
@@ -6735,15 +6735,15 @@
         <v>HRV</v>
       </c>
       <c r="Q61" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Croatia</v>
       </c>
       <c r="R61" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Croatia</v>
       </c>
       <c r="S61" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Croatia</v>
       </c>
     </row>
@@ -6795,15 +6795,15 @@
         <v>CUB</v>
       </c>
       <c r="Q62" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Cuba</v>
       </c>
       <c r="R62" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Cuba</v>
       </c>
       <c r="S62" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Cuba</v>
       </c>
     </row>
@@ -6856,15 +6856,15 @@
         <v>NLD</v>
       </c>
       <c r="Q63" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Netherlands (Kingdom of the)</v>
       </c>
       <c r="R63" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Curaçao</v>
       </c>
       <c r="S63" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Curaçao</v>
       </c>
     </row>
@@ -6916,15 +6916,15 @@
         <v>CYP</v>
       </c>
       <c r="Q64" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Cyprus</v>
       </c>
       <c r="R64" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Cyprus</v>
       </c>
       <c r="S64" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Cyprus</v>
       </c>
     </row>
@@ -6976,15 +6976,15 @@
         <v>CZE</v>
       </c>
       <c r="Q65" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Czechia</v>
       </c>
       <c r="R65" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Czechia</v>
       </c>
       <c r="S65" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Czechia</v>
       </c>
     </row>
@@ -7014,10 +7014,10 @@
         <v>789</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="K66" s="2">
         <v>0</v>
@@ -7028,15 +7028,15 @@
         <v>0</v>
       </c>
       <c r="Q66" t="e">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="R66" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>not in M49 standard (2025)</v>
       </c>
       <c r="S66" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Czechoslovakia (historic)</v>
       </c>
     </row>
@@ -7088,15 +7088,15 @@
         <v>PRK</v>
       </c>
       <c r="Q67" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Democratic People's Republic of Korea</v>
       </c>
       <c r="R67" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Democratic People's Republic of Korea</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.2">
@@ -7147,15 +7147,15 @@
         <v>COD</v>
       </c>
       <c r="Q68" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Democratic Republic of the Congo</v>
       </c>
       <c r="R68" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Democratic Republic of the Congo</v>
       </c>
       <c r="S68" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Democratic Republic of the Congo</v>
       </c>
     </row>
@@ -7207,15 +7207,15 @@
         <v>DNK</v>
       </c>
       <c r="Q69" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Denmark</v>
       </c>
       <c r="R69" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Denmark</v>
       </c>
       <c r="S69" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Denmark</v>
       </c>
     </row>
@@ -7267,15 +7267,15 @@
         <v>DJI</v>
       </c>
       <c r="Q70" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Djibouti</v>
       </c>
       <c r="R70" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Djibouti</v>
       </c>
       <c r="S70" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Djibouti</v>
       </c>
     </row>
@@ -7327,15 +7327,15 @@
         <v>DMA</v>
       </c>
       <c r="Q71" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Dominica</v>
       </c>
       <c r="R71" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Dominica</v>
       </c>
       <c r="S71" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Dominica</v>
       </c>
     </row>
@@ -7387,15 +7387,15 @@
         <v>DOM</v>
       </c>
       <c r="Q72" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Dominican Republic</v>
       </c>
       <c r="R72" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Dominican Republic</v>
       </c>
       <c r="S72" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Dominican Republic</v>
       </c>
     </row>
@@ -7447,15 +7447,15 @@
         <v>ECU</v>
       </c>
       <c r="Q73" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Ecuador</v>
       </c>
       <c r="R73" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Ecuador</v>
       </c>
       <c r="S73" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Ecuador</v>
       </c>
     </row>
@@ -7507,15 +7507,15 @@
         <v>EGY</v>
       </c>
       <c r="Q74" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Egypt</v>
       </c>
       <c r="R74" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Egypt</v>
       </c>
       <c r="S74" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Egypt</v>
       </c>
     </row>
@@ -7567,15 +7567,15 @@
         <v>SLV</v>
       </c>
       <c r="Q75" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>El Salvador</v>
       </c>
       <c r="R75" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>El Salvador</v>
       </c>
       <c r="S75" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>El Salvador</v>
       </c>
     </row>
@@ -7627,15 +7627,15 @@
         <v>GNQ</v>
       </c>
       <c r="Q76" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Equatorial Guinea</v>
       </c>
       <c r="R76" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Equatorial Guinea</v>
       </c>
       <c r="S76" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Equatorial Guinea</v>
       </c>
     </row>
@@ -7687,15 +7687,15 @@
         <v>ERI</v>
       </c>
       <c r="Q77" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Eritrea</v>
       </c>
       <c r="R77" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Eritrea</v>
       </c>
       <c r="S77" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Eritrea</v>
       </c>
     </row>
@@ -7747,15 +7747,15 @@
         <v>EST</v>
       </c>
       <c r="Q78" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Estonia</v>
       </c>
       <c r="R78" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Estonia</v>
       </c>
       <c r="S78" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Estonia</v>
       </c>
     </row>
@@ -7807,15 +7807,15 @@
         <v>SWZ</v>
       </c>
       <c r="Q79" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Eswatini</v>
       </c>
       <c r="R79" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Eswatini</v>
       </c>
       <c r="S79" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Eswatini</v>
       </c>
     </row>
@@ -7867,15 +7867,15 @@
         <v>ETH</v>
       </c>
       <c r="Q80" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Ethiopia</v>
       </c>
       <c r="R80" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Ethiopia</v>
       </c>
       <c r="S80" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Ethiopia</v>
       </c>
     </row>
@@ -7928,15 +7928,15 @@
         <v>GBR</v>
       </c>
       <c r="Q81" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R81" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Falkland Islands (Malvinas)</v>
       </c>
       <c r="S81" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Falkland Islands (Malvinas)</v>
       </c>
     </row>
@@ -7989,15 +7989,15 @@
         <v>DNK</v>
       </c>
       <c r="Q82" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Denmark</v>
       </c>
       <c r="R82" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Faroe Islands</v>
       </c>
       <c r="S82" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Faroe Islands</v>
       </c>
     </row>
@@ -8049,15 +8049,15 @@
         <v>FJI</v>
       </c>
       <c r="Q83" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Fiji</v>
       </c>
       <c r="R83" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Fiji</v>
       </c>
       <c r="S83" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Fiji</v>
       </c>
     </row>
@@ -8109,15 +8109,15 @@
         <v>FIN</v>
       </c>
       <c r="Q84" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Finland</v>
       </c>
       <c r="R84" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Finland</v>
       </c>
       <c r="S84" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Finland</v>
       </c>
     </row>
@@ -8169,15 +8169,15 @@
         <v>FRA</v>
       </c>
       <c r="Q85" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R85" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>France</v>
       </c>
       <c r="S85" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>France</v>
       </c>
     </row>
@@ -8230,15 +8230,15 @@
         <v>FRA</v>
       </c>
       <c r="Q86" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R86" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>French Guiana</v>
       </c>
       <c r="S86" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>French Guiana</v>
       </c>
     </row>
@@ -8291,15 +8291,15 @@
         <v>FRA</v>
       </c>
       <c r="Q87" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R87" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>French Polynesia</v>
       </c>
       <c r="S87" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>French Polynesia</v>
       </c>
     </row>
@@ -8352,15 +8352,15 @@
         <v>FRA</v>
       </c>
       <c r="Q88" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R88" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>French Southern Territories</v>
       </c>
       <c r="S88" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>French Southern Territories</v>
       </c>
     </row>
@@ -8412,15 +8412,15 @@
         <v>GAB</v>
       </c>
       <c r="Q89" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Gabon</v>
       </c>
       <c r="R89" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Gabon</v>
       </c>
       <c r="S89" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Gabon</v>
       </c>
     </row>
@@ -8472,15 +8472,15 @@
         <v>GMB</v>
       </c>
       <c r="Q90" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Gambia</v>
       </c>
       <c r="R90" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Gambia</v>
       </c>
       <c r="S90" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Gambia</v>
       </c>
     </row>
@@ -8532,15 +8532,15 @@
         <v>GEO</v>
       </c>
       <c r="Q91" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Georgia</v>
       </c>
       <c r="R91" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Georgia</v>
       </c>
       <c r="S91" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Georgia</v>
       </c>
     </row>
@@ -8592,15 +8592,15 @@
         <v>DEU</v>
       </c>
       <c r="Q92" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Germany</v>
       </c>
       <c r="R92" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Germany</v>
       </c>
       <c r="S92" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Germany</v>
       </c>
     </row>
@@ -8652,15 +8652,15 @@
         <v>GHA</v>
       </c>
       <c r="Q93" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Ghana</v>
       </c>
       <c r="R93" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Ghana</v>
       </c>
       <c r="S93" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Ghana</v>
       </c>
     </row>
@@ -8713,15 +8713,15 @@
         <v>GBR</v>
       </c>
       <c r="Q94" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R94" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Gibraltar</v>
       </c>
       <c r="S94" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Gibraltar</v>
       </c>
     </row>
@@ -8773,15 +8773,15 @@
         <v>GRC</v>
       </c>
       <c r="Q95" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Greece</v>
       </c>
       <c r="R95" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Greece</v>
       </c>
       <c r="S95" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Greece</v>
       </c>
     </row>
@@ -8834,15 +8834,15 @@
         <v>DNK</v>
       </c>
       <c r="Q96" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Denmark</v>
       </c>
       <c r="R96" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Greenland</v>
       </c>
       <c r="S96" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Greenland</v>
       </c>
     </row>
@@ -8894,15 +8894,15 @@
         <v>GRD</v>
       </c>
       <c r="Q97" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Grenada</v>
       </c>
       <c r="R97" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Grenada</v>
       </c>
       <c r="S97" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Grenada</v>
       </c>
     </row>
@@ -8955,15 +8955,15 @@
         <v>FRA</v>
       </c>
       <c r="Q98" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R98" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Guadeloupe</v>
       </c>
       <c r="S98" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Guadeloupe</v>
       </c>
     </row>
@@ -9016,15 +9016,15 @@
         <v>USA</v>
       </c>
       <c r="Q99" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United States of America</v>
       </c>
       <c r="R99" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Guam</v>
       </c>
       <c r="S99" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Guam</v>
       </c>
     </row>
@@ -9076,15 +9076,15 @@
         <v>GTM</v>
       </c>
       <c r="Q100" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Guatemala</v>
       </c>
       <c r="R100" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Guatemala</v>
       </c>
       <c r="S100" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Guatemala</v>
       </c>
     </row>
@@ -9137,15 +9137,15 @@
         <v>GBR</v>
       </c>
       <c r="Q101" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R101" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Guernsey</v>
       </c>
       <c r="S101" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Guernsey</v>
       </c>
     </row>
@@ -9197,15 +9197,15 @@
         <v>GIN</v>
       </c>
       <c r="Q102" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Guinea</v>
       </c>
       <c r="R102" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Guinea</v>
       </c>
       <c r="S102" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Guinea</v>
       </c>
     </row>
@@ -9257,15 +9257,15 @@
         <v>GNB</v>
       </c>
       <c r="Q103" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Guinea-Bissau</v>
       </c>
       <c r="R103" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Guinea-Bissau</v>
       </c>
       <c r="S103" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Guinea-Bissau</v>
       </c>
     </row>
@@ -9317,15 +9317,15 @@
         <v>GUY</v>
       </c>
       <c r="Q104" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Guyana</v>
       </c>
       <c r="R104" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Guyana</v>
       </c>
       <c r="S104" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Guyana</v>
       </c>
     </row>
@@ -9377,15 +9377,15 @@
         <v>HTI</v>
       </c>
       <c r="Q105" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Haiti</v>
       </c>
       <c r="R105" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Haiti</v>
       </c>
       <c r="S105" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Haiti</v>
       </c>
     </row>
@@ -9438,15 +9438,15 @@
         <v>AUS</v>
       </c>
       <c r="Q106" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Australia</v>
       </c>
       <c r="R106" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Heard Island and McDonald Islands</v>
       </c>
       <c r="S106" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Heard Island and McDonald Islands</v>
       </c>
     </row>
@@ -9496,15 +9496,15 @@
         <v>0</v>
       </c>
       <c r="Q107" t="e">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="R107" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Holy See</v>
       </c>
       <c r="S107" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Holy See</v>
       </c>
     </row>
@@ -9556,15 +9556,15 @@
         <v>HND</v>
       </c>
       <c r="Q108" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Honduras</v>
       </c>
       <c r="R108" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Honduras</v>
       </c>
       <c r="S108" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Honduras</v>
       </c>
     </row>
@@ -9616,15 +9616,15 @@
         <v>HUN</v>
       </c>
       <c r="Q109" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Hungary</v>
       </c>
       <c r="R109" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Hungary</v>
       </c>
       <c r="S109" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Hungary</v>
       </c>
     </row>
@@ -9676,15 +9676,15 @@
         <v>ISL</v>
       </c>
       <c r="Q110" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Iceland</v>
       </c>
       <c r="R110" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Iceland</v>
       </c>
       <c r="S110" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Iceland</v>
       </c>
     </row>
@@ -9736,15 +9736,15 @@
         <v>IND</v>
       </c>
       <c r="Q111" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>India</v>
       </c>
       <c r="R111" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>India</v>
       </c>
       <c r="S111" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>India</v>
       </c>
     </row>
@@ -9796,15 +9796,15 @@
         <v>IDN</v>
       </c>
       <c r="Q112" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Indonesia</v>
       </c>
       <c r="R112" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Indonesia</v>
       </c>
       <c r="S112" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Indonesia</v>
       </c>
     </row>
@@ -9856,15 +9856,15 @@
         <v>IRN</v>
       </c>
       <c r="Q113" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Iran (Islamic Republic of)</v>
       </c>
       <c r="R113" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Iran (Islamic Republic of)</v>
       </c>
       <c r="S113" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Iran (Islamic Republic of)</v>
       </c>
     </row>
@@ -9916,15 +9916,15 @@
         <v>IRQ</v>
       </c>
       <c r="Q114" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Iraq</v>
       </c>
       <c r="R114" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Iraq</v>
       </c>
       <c r="S114" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Iraq</v>
       </c>
     </row>
@@ -9976,15 +9976,15 @@
         <v>IRL</v>
       </c>
       <c r="Q115" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Ireland</v>
       </c>
       <c r="R115" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Ireland</v>
       </c>
       <c r="S115" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Ireland</v>
       </c>
     </row>
@@ -10037,15 +10037,15 @@
         <v>GBR</v>
       </c>
       <c r="Q116" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R116" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Isle of Man</v>
       </c>
       <c r="S116" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Isle of Man</v>
       </c>
     </row>
@@ -10097,15 +10097,15 @@
         <v>ISR</v>
       </c>
       <c r="Q117" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Israel</v>
       </c>
       <c r="R117" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Israel</v>
       </c>
       <c r="S117" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Israel</v>
       </c>
     </row>
@@ -10157,15 +10157,15 @@
         <v>ITA</v>
       </c>
       <c r="Q118" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Italy</v>
       </c>
       <c r="R118" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Italy</v>
       </c>
       <c r="S118" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Italy</v>
       </c>
     </row>
@@ -10217,15 +10217,15 @@
         <v>JAM</v>
       </c>
       <c r="Q119" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Jamaica</v>
       </c>
       <c r="R119" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Jamaica</v>
       </c>
       <c r="S119" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Jamaica</v>
       </c>
     </row>
@@ -10277,15 +10277,15 @@
         <v>JPN</v>
       </c>
       <c r="Q120" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Japan</v>
       </c>
       <c r="R120" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Japan</v>
       </c>
       <c r="S120" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Japan</v>
       </c>
     </row>
@@ -10338,15 +10338,15 @@
         <v>GBR</v>
       </c>
       <c r="Q121" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R121" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Jersey</v>
       </c>
       <c r="S121" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Jersey</v>
       </c>
     </row>
@@ -10398,15 +10398,15 @@
         <v>JOR</v>
       </c>
       <c r="Q122" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Jordan</v>
       </c>
       <c r="R122" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Jordan</v>
       </c>
       <c r="S122" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Jordan</v>
       </c>
     </row>
@@ -10458,15 +10458,15 @@
         <v>KAZ</v>
       </c>
       <c r="Q123" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Kazakhstan</v>
       </c>
       <c r="R123" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Kazakhstan</v>
       </c>
       <c r="S123" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Kazakhstan</v>
       </c>
     </row>
@@ -10518,15 +10518,15 @@
         <v>KEN</v>
       </c>
       <c r="Q124" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Kenya</v>
       </c>
       <c r="R124" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Kenya</v>
       </c>
       <c r="S124" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Kenya</v>
       </c>
     </row>
@@ -10578,15 +10578,15 @@
         <v>KIR</v>
       </c>
       <c r="Q125" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Kiribati</v>
       </c>
       <c r="R125" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Kiribati</v>
       </c>
       <c r="S125" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Kiribati</v>
       </c>
     </row>
@@ -10616,16 +10616,16 @@
         <v>789</v>
       </c>
       <c r="I126" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="J126" s="3" t="s">
         <v>814</v>
-      </c>
-      <c r="J126" s="3" t="s">
-        <v>816</v>
       </c>
       <c r="K126">
         <v>412</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="M126" s="3"/>
       <c r="P126">
@@ -10633,15 +10633,15 @@
         <v>0</v>
       </c>
       <c r="Q126" t="e">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="R126" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>not in M49 standard (2025)</v>
       </c>
       <c r="S126" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.2">
@@ -10692,15 +10692,15 @@
         <v>KWT</v>
       </c>
       <c r="Q127" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Kuwait</v>
       </c>
       <c r="R127" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Kuwait</v>
       </c>
       <c r="S127" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Kuwait</v>
       </c>
     </row>
@@ -10752,15 +10752,15 @@
         <v>KGZ</v>
       </c>
       <c r="Q128" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Kyrgyzstan</v>
       </c>
       <c r="R128" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Kyrgyzstan</v>
       </c>
       <c r="S128" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Kyrgyzstan</v>
       </c>
     </row>
@@ -10812,15 +10812,15 @@
         <v>LAO</v>
       </c>
       <c r="Q129" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Lao People's Democratic Republic</v>
       </c>
       <c r="R129" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Lao People's Democratic Republic</v>
       </c>
       <c r="S129" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Lao People's Democratic Republic</v>
       </c>
     </row>
@@ -10872,15 +10872,15 @@
         <v>LVA</v>
       </c>
       <c r="Q130" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Latvia</v>
       </c>
       <c r="R130" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Latvia</v>
       </c>
       <c r="S130" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Latvia</v>
       </c>
     </row>
@@ -10932,15 +10932,15 @@
         <v>LBN</v>
       </c>
       <c r="Q131" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Lebanon</v>
       </c>
       <c r="R131" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Lebanon</v>
       </c>
       <c r="S131" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Lebanon</v>
       </c>
     </row>
@@ -10992,15 +10992,15 @@
         <v>LSO</v>
       </c>
       <c r="Q132" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Lesotho</v>
       </c>
       <c r="R132" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Lesotho</v>
       </c>
       <c r="S132" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Lesotho</v>
       </c>
     </row>
@@ -11052,15 +11052,15 @@
         <v>LBR</v>
       </c>
       <c r="Q133" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Liberia</v>
       </c>
       <c r="R133" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Liberia</v>
       </c>
       <c r="S133" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Liberia</v>
       </c>
     </row>
@@ -11112,15 +11112,15 @@
         <v>LBY</v>
       </c>
       <c r="Q134" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Libya</v>
       </c>
       <c r="R134" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Libya</v>
       </c>
       <c r="S134" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Libya</v>
       </c>
     </row>
@@ -11172,15 +11172,15 @@
         <v>LIE</v>
       </c>
       <c r="Q135" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Liechtenstein</v>
       </c>
       <c r="R135" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Liechtenstein</v>
       </c>
       <c r="S135" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Liechtenstein</v>
       </c>
     </row>
@@ -11232,15 +11232,15 @@
         <v>LTU</v>
       </c>
       <c r="Q136" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Lithuania</v>
       </c>
       <c r="R136" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Lithuania</v>
       </c>
       <c r="S136" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Lithuania</v>
       </c>
     </row>
@@ -11292,15 +11292,15 @@
         <v>LUX</v>
       </c>
       <c r="Q137" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Luxembourg</v>
       </c>
       <c r="R137" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Luxembourg</v>
       </c>
       <c r="S137" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Luxembourg</v>
       </c>
     </row>
@@ -11352,15 +11352,15 @@
         <v>MDG</v>
       </c>
       <c r="Q138" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Madagascar</v>
       </c>
       <c r="R138" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Madagascar</v>
       </c>
       <c r="S138" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Madagascar</v>
       </c>
     </row>
@@ -11412,15 +11412,15 @@
         <v>MWI</v>
       </c>
       <c r="Q139" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Malawi</v>
       </c>
       <c r="R139" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Malawi</v>
       </c>
       <c r="S139" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Malawi</v>
       </c>
     </row>
@@ -11472,15 +11472,15 @@
         <v>MYS</v>
       </c>
       <c r="Q140" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Malaysia</v>
       </c>
       <c r="R140" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Malaysia</v>
       </c>
       <c r="S140" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Malaysia</v>
       </c>
     </row>
@@ -11532,15 +11532,15 @@
         <v>MDV</v>
       </c>
       <c r="Q141" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Maldives</v>
       </c>
       <c r="R141" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Maldives</v>
       </c>
       <c r="S141" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Maldives</v>
       </c>
     </row>
@@ -11592,15 +11592,15 @@
         <v>MLI</v>
       </c>
       <c r="Q142" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Mali</v>
       </c>
       <c r="R142" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Mali</v>
       </c>
       <c r="S142" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Mali</v>
       </c>
     </row>
@@ -11652,15 +11652,15 @@
         <v>MLT</v>
       </c>
       <c r="Q143" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Malta</v>
       </c>
       <c r="R143" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Malta</v>
       </c>
       <c r="S143" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Malta</v>
       </c>
     </row>
@@ -11712,15 +11712,15 @@
         <v>MHL</v>
       </c>
       <c r="Q144" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Marshall Islands</v>
       </c>
       <c r="R144" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Marshall Islands</v>
       </c>
       <c r="S144" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Marshall Islands</v>
       </c>
     </row>
@@ -11773,15 +11773,15 @@
         <v>FRA</v>
       </c>
       <c r="Q145" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R145" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Martinique</v>
       </c>
       <c r="S145" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Martinique</v>
       </c>
     </row>
@@ -11833,15 +11833,15 @@
         <v>MRT</v>
       </c>
       <c r="Q146" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Mauritania</v>
       </c>
       <c r="R146" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Mauritania</v>
       </c>
       <c r="S146" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Mauritania</v>
       </c>
     </row>
@@ -11893,15 +11893,15 @@
         <v>MUS</v>
       </c>
       <c r="Q147" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Mauritius</v>
       </c>
       <c r="R147" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Mauritius</v>
       </c>
       <c r="S147" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Mauritius</v>
       </c>
     </row>
@@ -11954,15 +11954,15 @@
         <v>FRA</v>
       </c>
       <c r="Q148" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R148" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Mayotte</v>
       </c>
       <c r="S148" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Mayotte</v>
       </c>
     </row>
@@ -12014,15 +12014,15 @@
         <v>MEX</v>
       </c>
       <c r="Q149" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Mexico</v>
       </c>
       <c r="R149" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Mexico</v>
       </c>
       <c r="S149" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Mexico</v>
       </c>
     </row>
@@ -12074,15 +12074,15 @@
         <v>FSM</v>
       </c>
       <c r="Q150" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Micronesia (Federated States of)</v>
       </c>
       <c r="R150" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Micronesia (Federated States of)</v>
       </c>
       <c r="S150" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.2">
@@ -12133,15 +12133,15 @@
         <v>MCO</v>
       </c>
       <c r="Q151" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Monaco</v>
       </c>
       <c r="R151" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Monaco</v>
       </c>
       <c r="S151" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Monaco</v>
       </c>
     </row>
@@ -12193,15 +12193,15 @@
         <v>MNG</v>
       </c>
       <c r="Q152" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Mongolia</v>
       </c>
       <c r="R152" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Mongolia</v>
       </c>
       <c r="S152" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Mongolia</v>
       </c>
     </row>
@@ -12253,15 +12253,15 @@
         <v>MNE</v>
       </c>
       <c r="Q153" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Montenegro</v>
       </c>
       <c r="R153" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Montenegro</v>
       </c>
       <c r="S153" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Montenegro</v>
       </c>
     </row>
@@ -12314,15 +12314,15 @@
         <v>GBR</v>
       </c>
       <c r="Q154" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R154" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Montserrat</v>
       </c>
       <c r="S154" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Montserrat</v>
       </c>
     </row>
@@ -12374,15 +12374,15 @@
         <v>MAR</v>
       </c>
       <c r="Q155" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Morocco</v>
       </c>
       <c r="R155" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Morocco</v>
       </c>
       <c r="S155" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Morocco</v>
       </c>
     </row>
@@ -12434,15 +12434,15 @@
         <v>MOZ</v>
       </c>
       <c r="Q156" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Mozambique</v>
       </c>
       <c r="R156" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Mozambique</v>
       </c>
       <c r="S156" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Mozambique</v>
       </c>
     </row>
@@ -12494,15 +12494,15 @@
         <v>MMR</v>
       </c>
       <c r="Q157" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Myanmar</v>
       </c>
       <c r="R157" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Myanmar</v>
       </c>
       <c r="S157" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Myanmar</v>
       </c>
     </row>
@@ -12554,15 +12554,15 @@
         <v>NAM</v>
       </c>
       <c r="Q158" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Namibia</v>
       </c>
       <c r="R158" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Namibia</v>
       </c>
       <c r="S158" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Namibia</v>
       </c>
     </row>
@@ -12614,15 +12614,15 @@
         <v>NRU</v>
       </c>
       <c r="Q159" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Nauru</v>
       </c>
       <c r="R159" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Nauru</v>
       </c>
       <c r="S159" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Nauru</v>
       </c>
     </row>
@@ -12674,15 +12674,15 @@
         <v>NPL</v>
       </c>
       <c r="Q160" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Nepal</v>
       </c>
       <c r="R160" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Nepal</v>
       </c>
       <c r="S160" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Nepal</v>
       </c>
     </row>
@@ -12734,15 +12734,15 @@
         <v>NLD</v>
       </c>
       <c r="Q161" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Netherlands (Kingdom of the)</v>
       </c>
       <c r="R161" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Netherlands (Kingdom of the)</v>
       </c>
       <c r="S161" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="162" spans="1:19" x14ac:dyDescent="0.2">
@@ -12771,10 +12771,10 @@
         <v>192</v>
       </c>
       <c r="I162" s="4" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="K162" s="2">
         <v>0</v>
@@ -12785,15 +12785,15 @@
         <v>0</v>
       </c>
       <c r="Q162" t="e">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="R162" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>not in M49 standard (2025)</v>
       </c>
       <c r="S162" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Netherlands Antilles (historic)</v>
       </c>
     </row>
@@ -12846,15 +12846,15 @@
         <v>FRA</v>
       </c>
       <c r="Q163" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R163" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>New Caledonia</v>
       </c>
       <c r="S163" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>New Caledonia</v>
       </c>
     </row>
@@ -12906,15 +12906,15 @@
         <v>NZL</v>
       </c>
       <c r="Q164" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>New Zealand</v>
       </c>
       <c r="R164" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>New Zealand</v>
       </c>
       <c r="S164" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>New Zealand</v>
       </c>
     </row>
@@ -12966,15 +12966,15 @@
         <v>NIC</v>
       </c>
       <c r="Q165" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Nicaragua</v>
       </c>
       <c r="R165" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Nicaragua</v>
       </c>
       <c r="S165" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Nicaragua</v>
       </c>
     </row>
@@ -13026,15 +13026,15 @@
         <v>NER</v>
       </c>
       <c r="Q166" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Niger</v>
       </c>
       <c r="R166" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Niger</v>
       </c>
       <c r="S166" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Niger</v>
       </c>
     </row>
@@ -13086,15 +13086,15 @@
         <v>NGA</v>
       </c>
       <c r="Q167" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Nigeria</v>
       </c>
       <c r="R167" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Nigeria</v>
       </c>
       <c r="S167" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Nigeria</v>
       </c>
     </row>
@@ -13147,15 +13147,15 @@
         <v>NZL</v>
       </c>
       <c r="Q168" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>New Zealand</v>
       </c>
       <c r="R168" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Niue</v>
       </c>
       <c r="S168" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Niue</v>
       </c>
     </row>
@@ -13208,15 +13208,15 @@
         <v>AUS</v>
       </c>
       <c r="Q169" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Australia</v>
       </c>
       <c r="R169" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Norfolk Island</v>
       </c>
       <c r="S169" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Norfolk Island</v>
       </c>
     </row>
@@ -13268,15 +13268,15 @@
         <v>MKD</v>
       </c>
       <c r="Q170" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>North Macedonia</v>
       </c>
       <c r="R170" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>North Macedonia</v>
       </c>
       <c r="S170" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>North Macedonia</v>
       </c>
     </row>
@@ -13329,15 +13329,15 @@
         <v>USA</v>
       </c>
       <c r="Q171" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United States of America</v>
       </c>
       <c r="R171" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Northern Mariana Islands</v>
       </c>
       <c r="S171" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Northern Mariana Islands</v>
       </c>
     </row>
@@ -13389,15 +13389,15 @@
         <v>NOR</v>
       </c>
       <c r="Q172" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Norway</v>
       </c>
       <c r="R172" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Norway</v>
       </c>
       <c r="S172" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Norway</v>
       </c>
     </row>
@@ -13449,15 +13449,15 @@
         <v>OMN</v>
       </c>
       <c r="Q173" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Oman</v>
       </c>
       <c r="R173" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Oman</v>
       </c>
       <c r="S173" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Oman</v>
       </c>
     </row>
@@ -13509,15 +13509,15 @@
         <v>PAK</v>
       </c>
       <c r="Q174" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Pakistan</v>
       </c>
       <c r="R174" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Pakistan</v>
       </c>
       <c r="S174" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Pakistan</v>
       </c>
     </row>
@@ -13569,15 +13569,15 @@
         <v>PLW</v>
       </c>
       <c r="Q175" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Palau</v>
       </c>
       <c r="R175" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Palau</v>
       </c>
       <c r="S175" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Palau</v>
       </c>
     </row>
@@ -13629,15 +13629,15 @@
         <v>PAN</v>
       </c>
       <c r="Q176" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Panama</v>
       </c>
       <c r="R176" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Panama</v>
       </c>
       <c r="S176" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Panama</v>
       </c>
     </row>
@@ -13689,15 +13689,15 @@
         <v>PNG</v>
       </c>
       <c r="Q177" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Papua New Guinea</v>
       </c>
       <c r="R177" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Papua New Guinea</v>
       </c>
       <c r="S177" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Papua New Guinea</v>
       </c>
     </row>
@@ -13749,15 +13749,15 @@
         <v>PRY</v>
       </c>
       <c r="Q178" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Paraguay</v>
       </c>
       <c r="R178" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Paraguay</v>
       </c>
       <c r="S178" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Paraguay</v>
       </c>
     </row>
@@ -13809,15 +13809,15 @@
         <v>PER</v>
       </c>
       <c r="Q179" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Peru</v>
       </c>
       <c r="R179" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Peru</v>
       </c>
       <c r="S179" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Peru</v>
       </c>
     </row>
@@ -13869,15 +13869,15 @@
         <v>PHL</v>
       </c>
       <c r="Q180" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Philippines</v>
       </c>
       <c r="R180" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Philippines</v>
       </c>
       <c r="S180" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Philippines</v>
       </c>
     </row>
@@ -13930,15 +13930,15 @@
         <v>GBR</v>
       </c>
       <c r="Q181" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R181" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Pitcairn</v>
       </c>
       <c r="S181" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Pitcairn</v>
       </c>
     </row>
@@ -13990,15 +13990,15 @@
         <v>POL</v>
       </c>
       <c r="Q182" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Poland</v>
       </c>
       <c r="R182" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Poland</v>
       </c>
       <c r="S182" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Poland</v>
       </c>
     </row>
@@ -14050,15 +14050,15 @@
         <v>PRT</v>
       </c>
       <c r="Q183" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Portugal</v>
       </c>
       <c r="R183" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Portugal</v>
       </c>
       <c r="S183" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Portugal</v>
       </c>
     </row>
@@ -14111,15 +14111,15 @@
         <v>USA</v>
       </c>
       <c r="Q184" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United States of America</v>
       </c>
       <c r="R184" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Puerto Rico</v>
       </c>
       <c r="S184" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Puerto Rico</v>
       </c>
     </row>
@@ -14171,15 +14171,15 @@
         <v>QAT</v>
       </c>
       <c r="Q185" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Qatar</v>
       </c>
       <c r="R185" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Qatar</v>
       </c>
       <c r="S185" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Qatar</v>
       </c>
     </row>
@@ -14231,15 +14231,15 @@
         <v>KOR</v>
       </c>
       <c r="Q186" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Republic of Korea</v>
       </c>
       <c r="R186" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Republic of Korea</v>
       </c>
       <c r="S186" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Republic of Korea</v>
       </c>
     </row>
@@ -14291,15 +14291,15 @@
         <v>MDA</v>
       </c>
       <c r="Q187" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Republic of Moldova</v>
       </c>
       <c r="R187" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Republic of Moldova</v>
       </c>
       <c r="S187" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Republic of Moldova</v>
       </c>
     </row>
@@ -14352,15 +14352,15 @@
         <v>FRA</v>
       </c>
       <c r="Q188" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R188" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Réunion</v>
       </c>
       <c r="S188" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Réunion</v>
       </c>
     </row>
@@ -14412,15 +14412,15 @@
         <v>ROU</v>
       </c>
       <c r="Q189" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Romania</v>
       </c>
       <c r="R189" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Romania</v>
       </c>
       <c r="S189" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Romania</v>
       </c>
     </row>
@@ -14472,15 +14472,15 @@
         <v>RUS</v>
       </c>
       <c r="Q190" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Russian Federation</v>
       </c>
       <c r="R190" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Russian Federation</v>
       </c>
       <c r="S190" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Russian Federation</v>
       </c>
     </row>
@@ -14532,15 +14532,15 @@
         <v>RWA</v>
       </c>
       <c r="Q191" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Rwanda</v>
       </c>
       <c r="R191" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Rwanda</v>
       </c>
       <c r="S191" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Rwanda</v>
       </c>
     </row>
@@ -14593,15 +14593,15 @@
         <v>FRA</v>
       </c>
       <c r="Q192" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R192" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Saint Barthélemy</v>
       </c>
       <c r="S192" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Saint Barthélemy</v>
       </c>
     </row>
@@ -14654,15 +14654,15 @@
         <v>GBR</v>
       </c>
       <c r="Q193" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R193" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Saint Helena</v>
       </c>
       <c r="S193" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Saint Helena</v>
       </c>
     </row>
@@ -14714,15 +14714,15 @@
         <v>KNA</v>
       </c>
       <c r="Q194" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Saint Kitts and Nevis</v>
       </c>
       <c r="R194" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Saint Kitts and Nevis</v>
       </c>
       <c r="S194" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Saint Kitts and Nevis</v>
       </c>
     </row>
@@ -14774,15 +14774,15 @@
         <v>LCA</v>
       </c>
       <c r="Q195" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Saint Lucia</v>
       </c>
       <c r="R195" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Saint Lucia</v>
       </c>
       <c r="S195" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Saint Lucia</v>
       </c>
     </row>
@@ -14835,15 +14835,15 @@
         <v>FRA</v>
       </c>
       <c r="Q196" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R196" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Saint Martin (French Part)</v>
       </c>
       <c r="S196" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="197" spans="1:19" x14ac:dyDescent="0.2">
@@ -14894,15 +14894,15 @@
         <v>FRA</v>
       </c>
       <c r="Q197" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R197" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Saint Pierre and Miquelon</v>
       </c>
       <c r="S197" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Saint Pierre and Miquelon</v>
       </c>
     </row>
@@ -14954,15 +14954,15 @@
         <v>VCT</v>
       </c>
       <c r="Q198" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Saint Vincent and the Grenadines</v>
       </c>
       <c r="R198" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Saint Vincent and the Grenadines</v>
       </c>
       <c r="S198" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Saint Vincent and the Grenadines</v>
       </c>
     </row>
@@ -15014,15 +15014,15 @@
         <v>WSM</v>
       </c>
       <c r="Q199" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Samoa</v>
       </c>
       <c r="R199" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Samoa</v>
       </c>
       <c r="S199" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Samoa</v>
       </c>
     </row>
@@ -15074,15 +15074,15 @@
         <v>SMR</v>
       </c>
       <c r="Q200" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>San Marino</v>
       </c>
       <c r="R200" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>San Marino</v>
       </c>
       <c r="S200" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>San Marino</v>
       </c>
     </row>
@@ -15134,15 +15134,15 @@
         <v>STP</v>
       </c>
       <c r="Q201" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Sao Tome and Principe</v>
       </c>
       <c r="R201" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Sao Tome and Principe</v>
       </c>
       <c r="S201" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Sao Tome and Principe</v>
       </c>
     </row>
@@ -15194,15 +15194,15 @@
         <v>SAU</v>
       </c>
       <c r="Q202" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Saudi Arabia</v>
       </c>
       <c r="R202" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Saudi Arabia</v>
       </c>
       <c r="S202" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Saudi Arabia</v>
       </c>
     </row>
@@ -15254,15 +15254,15 @@
         <v>SEN</v>
       </c>
       <c r="Q203" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Senegal</v>
       </c>
       <c r="R203" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Senegal</v>
       </c>
       <c r="S203" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Senegal</v>
       </c>
     </row>
@@ -15314,15 +15314,15 @@
         <v>SRB</v>
       </c>
       <c r="Q204" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Serbia</v>
       </c>
       <c r="R204" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Serbia</v>
       </c>
       <c r="S204" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Serbia</v>
       </c>
     </row>
@@ -15352,10 +15352,10 @@
         <v>791</v>
       </c>
       <c r="I205" s="4" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="K205" s="2">
         <v>0</v>
@@ -15366,15 +15366,15 @@
         <v>0</v>
       </c>
       <c r="Q205" t="e">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="R205" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>not in M49 standard (2025)</v>
       </c>
       <c r="S205" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Serbia Montenegro (historic)</v>
       </c>
     </row>
@@ -15426,15 +15426,15 @@
         <v>SYC</v>
       </c>
       <c r="Q206" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Seychelles</v>
       </c>
       <c r="R206" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Seychelles</v>
       </c>
       <c r="S206" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Seychelles</v>
       </c>
     </row>
@@ -15486,15 +15486,15 @@
         <v>SLE</v>
       </c>
       <c r="Q207" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Sierra Leone</v>
       </c>
       <c r="R207" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Sierra Leone</v>
       </c>
       <c r="S207" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Sierra Leone</v>
       </c>
     </row>
@@ -15546,15 +15546,15 @@
         <v>SGP</v>
       </c>
       <c r="Q208" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Singapore</v>
       </c>
       <c r="R208" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Singapore</v>
       </c>
       <c r="S208" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Singapore</v>
       </c>
     </row>
@@ -15606,15 +15606,15 @@
         <v>NLD</v>
       </c>
       <c r="Q209" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Netherlands (Kingdom of the)</v>
       </c>
       <c r="R209" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Sint Maarten (Dutch part)</v>
       </c>
       <c r="S209" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Sint Maarten (Dutch part)</v>
       </c>
     </row>
@@ -15666,15 +15666,15 @@
         <v>SVK</v>
       </c>
       <c r="Q210" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Slovakia</v>
       </c>
       <c r="R210" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Slovakia</v>
       </c>
       <c r="S210" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Slovakia</v>
       </c>
     </row>
@@ -15726,15 +15726,15 @@
         <v>SVN</v>
       </c>
       <c r="Q211" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Slovenia</v>
       </c>
       <c r="R211" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Slovenia</v>
       </c>
       <c r="S211" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Slovenia</v>
       </c>
     </row>
@@ -15786,15 +15786,15 @@
         <v>SLB</v>
       </c>
       <c r="Q212" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Solomon Islands</v>
       </c>
       <c r="R212" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Solomon Islands</v>
       </c>
       <c r="S212" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Solomon Islands</v>
       </c>
     </row>
@@ -15846,15 +15846,15 @@
         <v>SOM</v>
       </c>
       <c r="Q213" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Somalia</v>
       </c>
       <c r="R213" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Somalia</v>
       </c>
       <c r="S213" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Somalia</v>
       </c>
     </row>
@@ -15906,15 +15906,15 @@
         <v>ZAF</v>
       </c>
       <c r="Q214" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>South Africa</v>
       </c>
       <c r="R214" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>South Africa</v>
       </c>
       <c r="S214" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>South Africa</v>
       </c>
     </row>
@@ -15967,15 +15967,15 @@
         <v>GBR</v>
       </c>
       <c r="Q215" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R215" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>South Georgia and the South Sandwich Islands</v>
       </c>
       <c r="S215" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>South Georgia and the South Sandwich Islands</v>
       </c>
     </row>
@@ -16027,15 +16027,15 @@
         <v>SSD</v>
       </c>
       <c r="Q216" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>South Sudan</v>
       </c>
       <c r="R216" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>South Sudan</v>
       </c>
       <c r="S216" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>South Sudan</v>
       </c>
     </row>
@@ -16065,10 +16065,10 @@
         <v>789</v>
       </c>
       <c r="I217" s="4" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="K217" s="2">
         <v>0</v>
@@ -16079,15 +16079,15 @@
         <v>0</v>
       </c>
       <c r="Q217" t="e">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="R217" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>not in M49 standard (2025)</v>
       </c>
       <c r="S217" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Soviet Union (historic)</v>
       </c>
     </row>
@@ -16139,15 +16139,15 @@
         <v>ESP</v>
       </c>
       <c r="Q218" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Spain</v>
       </c>
       <c r="R218" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Spain</v>
       </c>
       <c r="S218" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Spain</v>
       </c>
     </row>
@@ -16199,15 +16199,15 @@
         <v>LKA</v>
       </c>
       <c r="Q219" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Sri Lanka</v>
       </c>
       <c r="R219" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Sri Lanka</v>
       </c>
       <c r="S219" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Sri Lanka</v>
       </c>
     </row>
@@ -16240,7 +16240,7 @@
         <v>512</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="K220" s="2">
         <v>275</v>
@@ -16257,15 +16257,15 @@
         <v>0</v>
       </c>
       <c r="Q220" t="e">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="R220" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>State of Palestine</v>
       </c>
       <c r="S220" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>State of Palestine</v>
       </c>
     </row>
@@ -16317,15 +16317,15 @@
         <v>SDN</v>
       </c>
       <c r="Q221" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Sudan</v>
       </c>
       <c r="R221" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Sudan</v>
       </c>
       <c r="S221" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Sudan</v>
       </c>
     </row>
@@ -16377,15 +16377,15 @@
         <v>SUR</v>
       </c>
       <c r="Q222" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Suriname</v>
       </c>
       <c r="R222" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Suriname</v>
       </c>
       <c r="S222" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Suriname</v>
       </c>
     </row>
@@ -16437,15 +16437,15 @@
         <v>NOR</v>
       </c>
       <c r="Q223" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Norway</v>
       </c>
       <c r="R223" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Svalbard and Jan Mayen Islands</v>
       </c>
       <c r="S223" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Svalbard and Jan Mayen Islands</v>
       </c>
     </row>
@@ -16497,15 +16497,15 @@
         <v>SWE</v>
       </c>
       <c r="Q224" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Sweden</v>
       </c>
       <c r="R224" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Sweden</v>
       </c>
       <c r="S224" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Sweden</v>
       </c>
     </row>
@@ -16557,15 +16557,15 @@
         <v>CHE</v>
       </c>
       <c r="Q225" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Switzerland</v>
       </c>
       <c r="R225" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Switzerland</v>
       </c>
       <c r="S225" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Switzerland</v>
       </c>
     </row>
@@ -16617,15 +16617,15 @@
         <v>SYR</v>
       </c>
       <c r="Q226" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Syrian Arab Republic</v>
       </c>
       <c r="R226" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Syrian Arab Republic</v>
       </c>
       <c r="S226" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Syrian Arab Republic</v>
       </c>
     </row>
@@ -16655,7 +16655,7 @@
         <v>797</v>
       </c>
       <c r="I227" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="J227" s="3" t="s">
         <v>798</v>
@@ -16671,15 +16671,15 @@
         <v>CHN</v>
       </c>
       <c r="Q227" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>China</v>
       </c>
       <c r="R227" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>not in M49 standard (2025)</v>
       </c>
       <c r="S227" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="228" spans="1:19" x14ac:dyDescent="0.2">
@@ -16730,15 +16730,15 @@
         <v>TJK</v>
       </c>
       <c r="Q228" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Tajikistan</v>
       </c>
       <c r="R228" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Tajikistan</v>
       </c>
       <c r="S228" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Tajikistan</v>
       </c>
     </row>
@@ -16790,15 +16790,15 @@
         <v>THA</v>
       </c>
       <c r="Q229" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Thailand</v>
       </c>
       <c r="R229" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Thailand</v>
       </c>
       <c r="S229" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Thailand</v>
       </c>
     </row>
@@ -16850,15 +16850,15 @@
         <v>TLS</v>
       </c>
       <c r="Q230" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Timor-Leste</v>
       </c>
       <c r="R230" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Timor-Leste</v>
       </c>
       <c r="S230" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Timor-Leste</v>
       </c>
     </row>
@@ -16910,15 +16910,15 @@
         <v>TGO</v>
       </c>
       <c r="Q231" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Togo</v>
       </c>
       <c r="R231" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Togo</v>
       </c>
       <c r="S231" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Togo</v>
       </c>
     </row>
@@ -16970,15 +16970,15 @@
         <v>NZL</v>
       </c>
       <c r="Q232" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>New Zealand</v>
       </c>
       <c r="R232" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Tokelau</v>
       </c>
       <c r="S232" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Tokelau</v>
       </c>
     </row>
@@ -17030,15 +17030,15 @@
         <v>TON</v>
       </c>
       <c r="Q233" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Tonga</v>
       </c>
       <c r="R233" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Tonga</v>
       </c>
       <c r="S233" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Tonga</v>
       </c>
     </row>
@@ -17090,15 +17090,15 @@
         <v>TTO</v>
       </c>
       <c r="Q234" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Trinidad and Tobago</v>
       </c>
       <c r="R234" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Trinidad and Tobago</v>
       </c>
       <c r="S234" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Trinidad and Tobago</v>
       </c>
     </row>
@@ -17150,15 +17150,15 @@
         <v>TUN</v>
       </c>
       <c r="Q235" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Tunisia</v>
       </c>
       <c r="R235" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Tunisia</v>
       </c>
       <c r="S235" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Tunisia</v>
       </c>
     </row>
@@ -17210,15 +17210,15 @@
         <v>TUR</v>
       </c>
       <c r="Q236" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Türkiye</v>
       </c>
       <c r="R236" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Türkiye</v>
       </c>
       <c r="S236" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Türkiye</v>
       </c>
     </row>
@@ -17270,15 +17270,15 @@
         <v>TKM</v>
       </c>
       <c r="Q237" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Turkmenistan</v>
       </c>
       <c r="R237" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Turkmenistan</v>
       </c>
       <c r="S237" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Turkmenistan</v>
       </c>
     </row>
@@ -17330,15 +17330,15 @@
         <v>GBR</v>
       </c>
       <c r="Q238" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R238" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Turks and Caicos Islands</v>
       </c>
       <c r="S238" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Turks and Caicos Islands</v>
       </c>
     </row>
@@ -17390,15 +17390,15 @@
         <v>TUV</v>
       </c>
       <c r="Q239" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Tuvalu</v>
       </c>
       <c r="R239" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Tuvalu</v>
       </c>
       <c r="S239" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Tuvalu</v>
       </c>
     </row>
@@ -17450,15 +17450,15 @@
         <v>UGA</v>
       </c>
       <c r="Q240" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Uganda</v>
       </c>
       <c r="R240" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Uganda</v>
       </c>
       <c r="S240" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Uganda</v>
       </c>
     </row>
@@ -17510,15 +17510,15 @@
         <v>UKR</v>
       </c>
       <c r="Q241" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Ukraine</v>
       </c>
       <c r="R241" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Ukraine</v>
       </c>
       <c r="S241" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Ukraine</v>
       </c>
     </row>
@@ -17570,15 +17570,15 @@
         <v>ARE</v>
       </c>
       <c r="Q242" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Arab Emirates</v>
       </c>
       <c r="R242" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>United Arab Emirates</v>
       </c>
       <c r="S242" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>United Arab Emirates</v>
       </c>
     </row>
@@ -17630,15 +17630,15 @@
         <v>GBR</v>
       </c>
       <c r="Q243" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="R243" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>United Kingdom of Great Britain and Northern Ireland</v>
       </c>
       <c r="S243" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="244" spans="1:19" x14ac:dyDescent="0.2">
@@ -17689,15 +17689,15 @@
         <v>TZA</v>
       </c>
       <c r="Q244" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United Republic of Tanzania</v>
       </c>
       <c r="R244" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>United Republic of Tanzania</v>
       </c>
       <c r="S244" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>United Republic of Tanzania</v>
       </c>
     </row>
@@ -17749,15 +17749,15 @@
         <v>USA</v>
       </c>
       <c r="Q245" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United States of America</v>
       </c>
       <c r="R245" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>United States Minor Outlying Islands</v>
       </c>
       <c r="S245" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>United States Minor Outlying Islands</v>
       </c>
     </row>
@@ -17809,15 +17809,15 @@
         <v>USA</v>
       </c>
       <c r="Q246" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United States of America</v>
       </c>
       <c r="R246" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>United States of America</v>
       </c>
       <c r="S246" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>United States of America</v>
       </c>
     </row>
@@ -17869,15 +17869,15 @@
         <v>USA</v>
       </c>
       <c r="Q247" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>United States of America</v>
       </c>
       <c r="R247" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>United States Virgin Islands</v>
       </c>
       <c r="S247" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>United States Virgin Islands</v>
       </c>
     </row>
@@ -17929,15 +17929,15 @@
         <v>URY</v>
       </c>
       <c r="Q248" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Uruguay</v>
       </c>
       <c r="R248" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Uruguay</v>
       </c>
       <c r="S248" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Uruguay</v>
       </c>
     </row>
@@ -17989,15 +17989,15 @@
         <v>UZB</v>
       </c>
       <c r="Q249" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Uzbekistan</v>
       </c>
       <c r="R249" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Uzbekistan</v>
       </c>
       <c r="S249" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Uzbekistan</v>
       </c>
     </row>
@@ -18049,15 +18049,15 @@
         <v>VUT</v>
       </c>
       <c r="Q250" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Vanuatu</v>
       </c>
       <c r="R250" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Vanuatu</v>
       </c>
       <c r="S250" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Vanuatu</v>
       </c>
     </row>
@@ -18109,15 +18109,15 @@
         <v>VEN</v>
       </c>
       <c r="Q251" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Venezuela (Bolivarian Republic of)</v>
       </c>
       <c r="R251" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Venezuela (Bolivarian Republic of)</v>
       </c>
       <c r="S251" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Venezuela (Bolivarian Republic of)</v>
       </c>
     </row>
@@ -18169,15 +18169,15 @@
         <v>VNM</v>
       </c>
       <c r="Q252" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Viet Nam</v>
       </c>
       <c r="R252" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Viet Nam</v>
       </c>
       <c r="S252" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Viet Nam</v>
       </c>
     </row>
@@ -18229,15 +18229,15 @@
         <v>FRA</v>
       </c>
       <c r="Q253" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>France</v>
       </c>
       <c r="R253" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Wallis and Futuna Islands</v>
       </c>
       <c r="S253" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Wallis and Futuna Islands</v>
       </c>
     </row>
@@ -18289,15 +18289,15 @@
         <v>MAR</v>
       </c>
       <c r="Q254" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Morocco</v>
       </c>
       <c r="R254" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Western Sahara</v>
       </c>
       <c r="S254" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Western Sahara</v>
       </c>
     </row>
@@ -18349,15 +18349,15 @@
         <v>YEM</v>
       </c>
       <c r="Q255" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Yemen</v>
       </c>
       <c r="R255" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Yemen</v>
       </c>
       <c r="S255" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Yemen</v>
       </c>
     </row>
@@ -18387,10 +18387,10 @@
         <v>791</v>
       </c>
       <c r="I256" s="4" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K256" s="2">
         <v>0</v>
@@ -18401,15 +18401,15 @@
         <v>0</v>
       </c>
       <c r="Q256" t="e">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="R256" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>not in M49 standard (2025)</v>
       </c>
       <c r="S256" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Yugoslavia (historic)</v>
       </c>
     </row>
@@ -18461,15 +18461,15 @@
         <v>ZMB</v>
       </c>
       <c r="Q257" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Zambia</v>
       </c>
       <c r="R257" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Zambia</v>
       </c>
       <c r="S257" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Zambia</v>
       </c>
     </row>
@@ -18521,15 +18521,15 @@
         <v>ZWE</v>
       </c>
       <c r="Q258" t="str">
-        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Country/Area]],2,FALSE)</f>
+        <f>VLOOKUP(Tabelle1[[#This Row],[Assist]],Tabelle1[[ISO-alpha3 Code]:[Area]],2,FALSE)</f>
         <v>Zimbabwe</v>
       </c>
       <c r="R258" t="str">
-        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Country/Area]],"not in M49 standard (2025)")</f>
+        <f>IF(Tabelle1[[#This Row],[M49]]="x",Tabelle1[[#This Row],[Area]],"not in M49 standard (2025)")</f>
         <v>Zimbabwe</v>
       </c>
       <c r="S258" t="str">
-        <f>Tabelle1[[#This Row],[Country/Area]]</f>
+        <f>Tabelle1[[#This Row],[Area]]</f>
         <v>Zimbabwe</v>
       </c>
     </row>
